--- a/api/1/clv2/xlsx/fr/Sector.xlsx
+++ b/api/1/clv2/xlsx/fr/Sector.xlsx
@@ -895,7 +895,7 @@
     <t>Droits de la personne</t>
   </si>
   <si>
-    <t>Mesures visant à aider les institutions et mécanismes spécialisés dans les droits de la personne opérant aux niveaux mondial, régional, national ou local, dans leur mission officielle de promotion et de protection des droits civils et politiques, économiques, sociaux et culturels tels que définis dans les conventions et pactes internationaux; transposition dans la législation nationale des engagements internationaux concernant les droits de la personne; notification et suivi; dialogue sur les droits de la personne. Défenseurs des droits de la personne et ONG oeuvrant dans ce domaine ; promotion des droits de la personne, défense active, mobilisation ; sensibilisation et éducation des citoyens aux droits de la personne. Élaboration de programmes concernant les droits de la personne ciblés sur des groupes particuliers comme les enfants, les individus en situation de handicap, les migrants, les minorités ethniques, religieuses, linguistiques et sexuelles, les populations autochtones et celles qui sont victimes de discrimination fondée sur la caste, les victimes de la traite d'êtres humains, les victimes de la torture. (Utiliser le code 15230 lorsque les activités se déroulent dans le cadre d'une opération internationale de maintien de la paix et le code 15180 pour les activités visant l'élimination de la violence à l'égard des femmes et des filles. Utiliser le code 15190 pour la programmation des droits de l'homme des réfugiés ou des migrants, y compris lorsqu'ils sont victimes de la traite d'êtres humains. Utiliser le code 16070 pour les activités concernant les Principes fondamentaux et Droits au travail, c'est-à-dire travail des enfants, travail forcé, non-discrimination dans l'emploi et le travail, liberté syndicale et négociation collective.)</t>
+    <t>Mesures visant à aider les institutions et mécanismes spécialisés dans les droits de la personne opérant aux niveaux mondial, régional, national ou local, dans leur mission officielle de promotion et de protection des droits civils et politiques, économiques, sociaux et culturels tels que définis dans les conventions et pactes internationaux; transposition dans la législation nationale des engagements internationaux concernant les droits de la personne; notification et suivi; dialogue sur les droits de la personne. Défenseurs des droits de la personne et ONG oeuvrant dans ce domaine ; promotion des droits de la personne, défense active, mobilisation ; sensibilisation et éducation des citoyens aux droits de la personne. Élaboration de programmes concernant les droits de la personne ciblés sur des groupes particuliers comme les enfants, les individus en situation de handicap, les minorités ethniques, religieuses, linguistiques et sexuelles, les populations autochtones et celles qui sont victimes de discrimination fondée sur la caste, les victimes de la traite d'êtres humains, les victimes de la torture. (Utiliser le code 15230 lorsque les activités se déroulent dans le cadre d'une opération internationale de maintien de la paix et le code 15180 pour les activités visant l'élimination de la violence à l'égard des femmes et des filles. Utiliser le code 15190 pour la programmation des droits de l'homme des réfugiés ou des migrants, y compris lorsqu'ils sont victimes de la traite d'êtres humains. Utiliser le code 16070 pour les activités concernant les Principes fondamentaux et Droits au travail, c'est-à-dire travail des enfants, travail forcé, non-discrimination dans l'emploi et le travail, liberté syndicale et négociation collective.)</t>
   </si>
   <si>
     <t>15161</t>
@@ -1858,7 +1858,7 @@
     <t>Facilitation, promotion et optimisation des transferts de fonds des migrants</t>
   </si>
   <si>
-    <t>Comprend les programmes visant à réduire les coûts des transferts de fonds des migrants, dont les coûts d'envoi, de transmission et de réception ainsi que les programmes les encourageant et/ou augmentant leur impact sur le développement. Le soutien au renforcement des capacités statistiques visant à en améliorer les données est à enregistrer sous le code 16062. La recherche sur le potentiel de développement des transferts de fonds des migrants est à enregistrer sous le code 43082.</t>
+    <t>Comprend les programmes visant à réduire les coûts des transferts de fonds des migrants.</t>
   </si>
   <si>
     <t>24081</t>
@@ -1891,7 +1891,7 @@
     <t>25030</t>
   </si>
   <si>
-    <t>Business development services</t>
+    <t>Services pour le développement des entreprises</t>
   </si>
   <si>
     <t>Fourniture de services publics et privés pour le développement des entreprises, par ex. incubateurs, stratégies d’entreprises, programmes de liens commerciaux et services de mise en relations. Cela comprend le soutien aux organisations privées représentant les entreprises, par ex. association d’entreprises ; chambres de commerce ; associations de producteurs ; fournisseurs de savoir faire et autres services d’aide au développement des entreprises. Pour les services financiers utiliser les codes 24030 ou 24040. Pour le développement des PME et pour le soutien aux sociétés dans le secteur industriel, utiliser les codes 32130 à 32172. Pour le soutien aux sociétés du secteur agricole utiliser le code 31120.</t>
@@ -2308,7 +2308,7 @@
     <t>32174</t>
   </si>
   <si>
-    <t>Production d'appareils de cuisine propres</t>
+    <t>Production d'appareils de cuisine propres, développement du marché et distribution</t>
   </si>
   <si>
     <t>Comprend la fabrication et la distribution de fours efficaces à biomasse, gazéifieurs, fours à biocarburants liquides, fours solaires, fours à gaz et bio gaz fours électriques</t>
